--- a/TestData/UITestData.xlsx
+++ b/TestData/UITestData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Credential" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="51">
   <si>
     <t>Username</t>
   </si>
@@ -90,9 +90,6 @@
     <t>Branch</t>
   </si>
   <si>
-    <t>24AAICA0488M1ZF</t>
-  </si>
-  <si>
     <t>Branch Sub-Type dropdown option</t>
   </si>
   <si>
@@ -139,13 +136,46 @@
   </si>
   <si>
     <t>VIJAY</t>
+  </si>
+  <si>
+    <t>Suspended GSTIN</t>
+  </si>
+  <si>
+    <t>Cancelled GSTIN</t>
+  </si>
+  <si>
+    <t>02AAGFA5896G1ZG</t>
+  </si>
+  <si>
+    <t>Invalid checksum GSTIN</t>
+  </si>
+  <si>
+    <t>GSTIN less than 15 characters</t>
+  </si>
+  <si>
+    <t>GSTIN more than 15 characters</t>
+  </si>
+  <si>
+    <t>27ABCDE1234F1Z5</t>
+  </si>
+  <si>
+    <t>27ABCDE1234F1Z</t>
+  </si>
+  <si>
+    <t>27ABCDE1234F1Z55</t>
+  </si>
+  <si>
+    <t>21AAACB9760D1Z2</t>
+  </si>
+  <si>
+    <t>07AACCU0153D1ZU</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -160,6 +190,10 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -169,10 +203,21 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB7B7B7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB7B7B7"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -185,11 +230,14 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -502,7 +550,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>2</v>
@@ -518,7 +566,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:U11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.28515625" customWidth="1"/>
@@ -536,10 +584,14 @@
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="32.28515625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="32" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="31.28515625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="27" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="27.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:21">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -583,18 +635,33 @@
         <v>21</v>
       </c>
       <c r="O1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16">
+        <v>38</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>40</v>
+      </c>
+      <c r="R1" t="s">
+        <v>41</v>
+      </c>
+      <c r="S1" t="s">
+        <v>43</v>
+      </c>
+      <c r="T1" t="s">
+        <v>44</v>
+      </c>
+      <c r="U1" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21">
       <c r="A2" t="s">
         <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C2" t="s">
         <v>14</v>
@@ -633,67 +700,82 @@
         <v>22</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="3" spans="1:16">
+      <c r="Q2" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" t="s">
+        <v>42</v>
+      </c>
+      <c r="S2" t="s">
+        <v>46</v>
+      </c>
+      <c r="T2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21">
       <c r="O3" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21">
       <c r="O4" s="2" t="s">
         <v>23</v>
       </c>
       <c r="P4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21">
+      <c r="O5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
-      <c r="O5" s="2" t="s">
+    <row r="6" spans="1:21">
+      <c r="O6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="P5" t="s">
+      <c r="P6" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
-      <c r="O6" s="2" t="s">
+    <row r="7" spans="1:21">
+      <c r="O7" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="P6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16">
-      <c r="O7" s="2" t="s">
+    </row>
+    <row r="8" spans="1:21">
+      <c r="O8" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:16">
-      <c r="O8" s="2" t="s">
+    <row r="9" spans="1:21">
+      <c r="O9" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
-      <c r="O9" s="2" t="s">
+    <row r="10" spans="1:21">
+      <c r="O10" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:16">
-      <c r="O10" s="2" t="s">
+    <row r="11" spans="1:21">
+      <c r="O11" s="2" t="s">
         <v>33</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16">
-      <c r="O11" s="2" t="s">
-        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/UITestData.xlsx
+++ b/TestData/UITestData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="Credential" sheetId="1" r:id="rId1"/>
@@ -24,9 +24,6 @@
     <t>Password</t>
   </si>
   <si>
-    <t>Kuchbhi@123</t>
-  </si>
-  <si>
     <t>Branch Sub-Type</t>
   </si>
   <si>
@@ -135,9 +132,6 @@
     <t>Branch Floor dropdown option</t>
   </si>
   <si>
-    <t>VIJAY</t>
-  </si>
-  <si>
     <t>Suspended GSTIN</t>
   </si>
   <si>
@@ -169,6 +163,12 @@
   </si>
   <si>
     <t>07AACCU0153D1ZU</t>
+  </si>
+  <si>
+    <t>Vijay@123</t>
+  </si>
+  <si>
+    <t>Vijay.kumar</t>
   </si>
 </sst>
 </file>
@@ -550,10 +550,10 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>2</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -593,93 +593,93 @@
   <sheetData>
     <row r="1" spans="1:21">
       <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>5</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>6</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>7</v>
       </c>
-      <c r="F1" t="s">
-        <v>8</v>
-      </c>
       <c r="G1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" t="s">
         <v>16</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>17</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>18</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>19</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>20</v>
       </c>
-      <c r="N1" t="s">
-        <v>21</v>
-      </c>
       <c r="O1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q1" t="s">
         <v>38</v>
       </c>
-      <c r="Q1" t="s">
-        <v>40</v>
-      </c>
       <c r="R1" t="s">
+        <v>39</v>
+      </c>
+      <c r="S1" t="s">
         <v>41</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U1" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="T1" t="s">
-        <v>44</v>
-      </c>
-      <c r="U1" s="3" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:21">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D2">
         <v>9237937388</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -697,85 +697,85 @@
         <v>1</v>
       </c>
       <c r="N2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="R2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="S2" t="s">
+        <v>44</v>
+      </c>
+      <c r="T2" t="s">
+        <v>45</v>
+      </c>
+      <c r="U2" t="s">
         <v>46</v>
-      </c>
-      <c r="T2" t="s">
-        <v>47</v>
-      </c>
-      <c r="U2" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:21">
       <c r="O3" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:21">
       <c r="O4" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:21">
       <c r="O5" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:21">
       <c r="O6" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:21">
       <c r="O7" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:21">
       <c r="O8" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:21">
       <c r="O9" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:21">
       <c r="O10" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:21">
       <c r="O11" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
